--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129322600</v>
+        <v>129321919</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506762</v>
+        <v>506804</v>
       </c>
       <c r="R3" t="n">
-        <v>6708250</v>
+        <v>6708310</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129321919</v>
+        <v>129322600</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506804</v>
+        <v>506762</v>
       </c>
       <c r="R4" t="n">
-        <v>6708310</v>
+        <v>6708250</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1113,45 +1113,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129323585</v>
+        <v>129323344</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506744</v>
+        <v>506712</v>
       </c>
       <c r="R6" t="n">
-        <v>6708266</v>
+        <v>6708322</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1207,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>100+</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,59 +1239,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129323344</v>
+        <v>129323585</v>
       </c>
       <c r="B7" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506712</v>
+        <v>506744</v>
       </c>
       <c r="R7" t="n">
-        <v>6708322</v>
+        <v>6708266</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,12 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>100+</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1453,7 +1453,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129323531</v>
+        <v>129321871</v>
       </c>
       <c r="B9" t="n">
         <v>98678</v>
@@ -1481,17 +1481,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506781</v>
+        <v>506794</v>
       </c>
       <c r="R9" t="n">
-        <v>6708313</v>
+        <v>6708308</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1547,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Över ca 1kvm, rikligt, 150+.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,7 +1579,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129321871</v>
+        <v>129323531</v>
       </c>
       <c r="B10" t="n">
         <v>98678</v>
@@ -1588,31 +1607,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506794</v>
+        <v>506781</v>
       </c>
       <c r="R10" t="n">
-        <v>6708308</v>
+        <v>6708313</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1654,12 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Över ca 1kvm, rikligt, 150+.</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2152,45 +2152,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129323543</v>
+        <v>129321922</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506765</v>
+        <v>506804</v>
       </c>
       <c r="R15" t="n">
-        <v>6708286</v>
+        <v>6708310</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2227,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2232,7 +2237,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2259,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129321922</v>
+        <v>129323053</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2270,39 +2280,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506804</v>
+        <v>506715</v>
       </c>
       <c r="R16" t="n">
-        <v>6708310</v>
+        <v>6708225</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2334,7 +2339,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2344,12 +2349,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2376,7 +2376,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129323053</v>
+        <v>129322456</v>
       </c>
       <c r="B17" t="n">
         <v>79041</v>
@@ -2407,14 +2407,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506715</v>
+        <v>506778</v>
       </c>
       <c r="R17" t="n">
-        <v>6708225</v>
+        <v>6708282</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2456,7 +2456,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2483,32 +2488,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129322456</v>
+        <v>129323543</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2518,10 +2523,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506778</v>
+        <v>506765</v>
       </c>
       <c r="R18" t="n">
-        <v>6708282</v>
+        <v>6708286</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2553,7 +2558,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2563,12 +2568,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3154,7 +3154,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129323598</v>
+        <v>129321974</v>
       </c>
       <c r="B24" t="n">
         <v>98678</v>
@@ -3183,16 +3183,20 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506737</v>
+        <v>506804</v>
       </c>
       <c r="R24" t="n">
-        <v>6708251</v>
+        <v>6708309</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3224,7 +3228,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3234,7 +3238,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3243,6 +3247,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3261,7 +3266,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129323359</v>
+        <v>129323598</v>
       </c>
       <c r="B25" t="n">
         <v>98678</v>
@@ -3289,31 +3294,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506713</v>
+        <v>506737</v>
       </c>
       <c r="R25" t="n">
-        <v>6708323</v>
+        <v>6708251</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3345,7 +3336,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3355,12 +3346,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3499,45 +3485,59 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129322464</v>
+        <v>129323359</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506779</v>
+        <v>506713</v>
       </c>
       <c r="R27" t="n">
-        <v>6708280</v>
+        <v>6708323</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3611,7 +3611,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129322521</v>
+        <v>129322464</v>
       </c>
       <c r="B28" t="n">
         <v>79041</v>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506769</v>
+        <v>506779</v>
       </c>
       <c r="R28" t="n">
-        <v>6708266</v>
+        <v>6708280</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3723,10 +3723,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129322534</v>
+        <v>129322521</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3734,39 +3734,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506774</v>
+        <v>506769</v>
       </c>
       <c r="R29" t="n">
-        <v>6708265</v>
+        <v>6708266</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3798,7 +3793,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3808,12 +3803,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre och färska.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3840,10 +3835,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129321673</v>
+        <v>129322534</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,34 +3846,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506735</v>
+        <v>506774</v>
       </c>
       <c r="R30" t="n">
-        <v>6708332</v>
+        <v>6708265</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3920,12 +3920,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Äldre och färska.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3949,6 +3949,118 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129321673</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>506735</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6708332</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -1686,59 +1686,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129321663</v>
+        <v>129321725</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506726</v>
+        <v>506758</v>
       </c>
       <c r="R11" t="n">
-        <v>6708333</v>
+        <v>6708321</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,12 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ca 50+ bladrosetter, en överblommad.</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,45 +1793,59 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129321725</v>
+        <v>129321663</v>
       </c>
       <c r="B12" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506758</v>
+        <v>506726</v>
       </c>
       <c r="R12" t="n">
-        <v>6708321</v>
+        <v>6708333</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,7 +1887,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 50+ bladrosetter, en överblommad.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2152,10 +2152,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129321922</v>
+        <v>129323053</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2163,39 +2163,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506804</v>
+        <v>506715</v>
       </c>
       <c r="R15" t="n">
-        <v>6708310</v>
+        <v>6708225</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2227,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2237,12 +2232,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2269,7 +2259,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129323053</v>
+        <v>129322456</v>
       </c>
       <c r="B16" t="n">
         <v>79041</v>
@@ -2300,14 +2290,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506715</v>
+        <v>506778</v>
       </c>
       <c r="R16" t="n">
-        <v>6708225</v>
+        <v>6708282</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2339,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2349,7 +2339,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2376,32 +2371,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129322456</v>
+        <v>129323543</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2411,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506778</v>
+        <v>506765</v>
       </c>
       <c r="R17" t="n">
-        <v>6708282</v>
+        <v>6708286</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2446,7 +2441,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2456,12 +2451,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2488,45 +2478,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129323543</v>
+        <v>129321922</v>
       </c>
       <c r="B18" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506765</v>
+        <v>506804</v>
       </c>
       <c r="R18" t="n">
-        <v>6708286</v>
+        <v>6708310</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,7 +2553,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2568,7 +2563,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129321919</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1113,59 +1113,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129323344</v>
+        <v>129323585</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506712</v>
+        <v>506744</v>
       </c>
       <c r="R6" t="n">
-        <v>6708322</v>
+        <v>6708266</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,12 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>100+</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129323585</v>
+        <v>129323568</v>
       </c>
       <c r="B7" t="n">
         <v>79041</v>
@@ -1274,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506744</v>
+        <v>506758</v>
       </c>
       <c r="R7" t="n">
-        <v>6708266</v>
+        <v>6708281</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,45 +1327,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129323568</v>
+        <v>129323344</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506758</v>
+        <v>506712</v>
       </c>
       <c r="R8" t="n">
-        <v>6708281</v>
+        <v>6708322</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1421,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>100+</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,7 +1456,7 @@
         <v>129321871</v>
       </c>
       <c r="B9" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>129323531</v>
       </c>
       <c r="B10" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>129321725</v>
       </c>
       <c r="B11" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>129321663</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>129321796</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2371,45 +2371,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129323543</v>
+        <v>129321922</v>
       </c>
       <c r="B17" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506765</v>
+        <v>506804</v>
       </c>
       <c r="R17" t="n">
-        <v>6708286</v>
+        <v>6708310</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2441,7 +2446,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2451,7 +2456,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2478,50 +2488,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129321922</v>
+        <v>129323543</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506804</v>
+        <v>506765</v>
       </c>
       <c r="R18" t="n">
-        <v>6708310</v>
+        <v>6708286</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2553,7 +2558,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2563,12 +2568,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2924,7 +2924,7 @@
         <v>129321689</v>
       </c>
       <c r="B22" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>129321974</v>
       </c>
       <c r="B24" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>129323598</v>
       </c>
       <c r="B25" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>129323359</v>
       </c>
       <c r="B27" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129321919</v>
+        <v>129322600</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506804</v>
+        <v>506762</v>
       </c>
       <c r="R3" t="n">
-        <v>6708310</v>
+        <v>6708250</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129322600</v>
+        <v>129321919</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506762</v>
+        <v>506804</v>
       </c>
       <c r="R4" t="n">
-        <v>6708250</v>
+        <v>6708310</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,12 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1113,45 +1113,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129323585</v>
+        <v>129323344</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506744</v>
+        <v>506712</v>
       </c>
       <c r="R6" t="n">
-        <v>6708266</v>
+        <v>6708322</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1207,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>100+</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1239,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129323568</v>
+        <v>129323585</v>
       </c>
       <c r="B7" t="n">
         <v>79041</v>
@@ -1255,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506758</v>
+        <v>506744</v>
       </c>
       <c r="R7" t="n">
-        <v>6708281</v>
+        <v>6708266</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,59 +1346,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129323344</v>
+        <v>129323568</v>
       </c>
       <c r="B8" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506712</v>
+        <v>506758</v>
       </c>
       <c r="R8" t="n">
-        <v>6708322</v>
+        <v>6708281</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,12 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>100+</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,7 +1456,7 @@
         <v>129321871</v>
       </c>
       <c r="B9" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>129323531</v>
       </c>
       <c r="B10" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>129321663</v>
       </c>
       <c r="B12" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>129321796</v>
       </c>
       <c r="B14" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,45 +2152,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129323053</v>
+        <v>129323543</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506715</v>
+        <v>506765</v>
       </c>
       <c r="R15" t="n">
-        <v>6708225</v>
+        <v>6708286</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2259,10 +2259,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129322456</v>
+        <v>129321922</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2270,34 +2270,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506778</v>
+        <v>506804</v>
       </c>
       <c r="R16" t="n">
-        <v>6708282</v>
+        <v>6708310</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,7 +2334,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,12 +2344,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,10 +2376,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129321922</v>
+        <v>129323053</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2382,39 +2387,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506804</v>
+        <v>506715</v>
       </c>
       <c r="R17" t="n">
-        <v>6708310</v>
+        <v>6708225</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2456,12 +2456,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2488,32 +2483,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129323543</v>
+        <v>129322456</v>
       </c>
       <c r="B18" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2523,10 +2518,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506765</v>
+        <v>506778</v>
       </c>
       <c r="R18" t="n">
-        <v>6708286</v>
+        <v>6708282</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,7 +2553,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2568,7 +2563,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2707,7 +2707,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129323677</v>
+        <v>129323106</v>
       </c>
       <c r="B20" t="n">
         <v>79041</v>
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506724</v>
+        <v>506720</v>
       </c>
       <c r="R20" t="n">
-        <v>6708250</v>
+        <v>6708241</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,7 +2814,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129323106</v>
+        <v>129323677</v>
       </c>
       <c r="B21" t="n">
         <v>79041</v>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506720</v>
+        <v>506724</v>
       </c>
       <c r="R21" t="n">
-        <v>6708241</v>
+        <v>6708250</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,7 +2924,7 @@
         <v>129321689</v>
       </c>
       <c r="B22" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>129321974</v>
       </c>
       <c r="B24" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>129323598</v>
       </c>
       <c r="B25" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3373,45 +3373,59 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129321706</v>
+        <v>129323359</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506741</v>
+        <v>506713</v>
       </c>
       <c r="R26" t="n">
-        <v>6708320</v>
+        <v>6708323</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3443,7 +3457,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3453,12 +3467,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3485,59 +3499,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129323359</v>
+        <v>129321706</v>
       </c>
       <c r="B27" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506713</v>
+        <v>506741</v>
       </c>
       <c r="R27" t="n">
-        <v>6708323</v>
+        <v>6708320</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>129321919</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1113,59 +1113,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129323344</v>
+        <v>129323568</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506712</v>
+        <v>506758</v>
       </c>
       <c r="R6" t="n">
-        <v>6708322</v>
+        <v>6708281</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,12 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>100+</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,45 +1220,59 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129323585</v>
+        <v>129323344</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506744</v>
+        <v>506712</v>
       </c>
       <c r="R7" t="n">
-        <v>6708266</v>
+        <v>6708322</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1314,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>100+</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,7 +1346,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129323568</v>
+        <v>129323585</v>
       </c>
       <c r="B8" t="n">
         <v>79041</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506758</v>
+        <v>506744</v>
       </c>
       <c r="R8" t="n">
-        <v>6708281</v>
+        <v>6708266</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,7 +1456,7 @@
         <v>129321871</v>
       </c>
       <c r="B9" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>129323531</v>
       </c>
       <c r="B10" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>129321663</v>
       </c>
       <c r="B12" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>129321796</v>
       </c>
       <c r="B14" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>129323543</v>
       </c>
       <c r="B15" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129321922</v>
+        <v>129322456</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2270,39 +2270,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506804</v>
+        <v>506778</v>
       </c>
       <c r="R16" t="n">
-        <v>6708310</v>
+        <v>6708282</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2334,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2344,12 +2339,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2376,10 +2371,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129323053</v>
+        <v>129321922</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,34 +2382,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506715</v>
+        <v>506804</v>
       </c>
       <c r="R17" t="n">
-        <v>6708225</v>
+        <v>6708310</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2456,7 +2456,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2483,7 +2488,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129322456</v>
+        <v>129323053</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2514,14 +2519,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506778</v>
+        <v>506715</v>
       </c>
       <c r="R18" t="n">
-        <v>6708282</v>
+        <v>6708225</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2553,7 +2558,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2563,12 +2568,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2707,7 +2707,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129323106</v>
+        <v>129323677</v>
       </c>
       <c r="B20" t="n">
         <v>79041</v>
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506720</v>
+        <v>506724</v>
       </c>
       <c r="R20" t="n">
-        <v>6708241</v>
+        <v>6708250</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,7 +2814,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129323677</v>
+        <v>129323106</v>
       </c>
       <c r="B21" t="n">
         <v>79041</v>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506724</v>
+        <v>506720</v>
       </c>
       <c r="R21" t="n">
-        <v>6708250</v>
+        <v>6708241</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,7 +2924,7 @@
         <v>129321689</v>
       </c>
       <c r="B22" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>129321974</v>
       </c>
       <c r="B24" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>129323598</v>
       </c>
       <c r="B25" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>129323359</v>
       </c>
       <c r="B26" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129321790</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129322600</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129321919</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129322635</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129323568</v>
+        <v>129323585</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506758</v>
+        <v>506744</v>
       </c>
       <c r="R6" t="n">
-        <v>6708281</v>
+        <v>6708266</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,59 +1220,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129323344</v>
+        <v>129323568</v>
       </c>
       <c r="B7" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506712</v>
+        <v>506758</v>
       </c>
       <c r="R7" t="n">
-        <v>6708322</v>
+        <v>6708281</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,12 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>100+</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,45 +1327,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129323585</v>
+        <v>129323344</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506744</v>
+        <v>506712</v>
       </c>
       <c r="R8" t="n">
-        <v>6708266</v>
+        <v>6708322</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1421,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>100+</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,7 +1456,7 @@
         <v>129321871</v>
       </c>
       <c r="B9" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>129323531</v>
       </c>
       <c r="B10" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,45 +1686,59 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129321725</v>
+        <v>129321663</v>
       </c>
       <c r="B11" t="n">
-        <v>91540</v>
+        <v>98710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506758</v>
+        <v>506726</v>
       </c>
       <c r="R11" t="n">
-        <v>6708321</v>
+        <v>6708333</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1780,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca 50+ bladrosetter, en överblommad.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,59 +1812,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129321663</v>
+        <v>129321725</v>
       </c>
       <c r="B12" t="n">
-        <v>98706</v>
+        <v>91543</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506726</v>
+        <v>506758</v>
       </c>
       <c r="R12" t="n">
-        <v>6708333</v>
+        <v>6708321</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,7 +1882,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1887,12 +1892,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 50+ bladrosetter, en överblommad.</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,7 +1922,7 @@
         <v>129323560</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>129321796</v>
       </c>
       <c r="B14" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,45 +2152,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129323543</v>
+        <v>129323053</v>
       </c>
       <c r="B15" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506765</v>
+        <v>506715</v>
       </c>
       <c r="R15" t="n">
-        <v>6708286</v>
+        <v>6708225</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2259,32 +2259,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129322456</v>
+        <v>129323543</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506778</v>
+        <v>506765</v>
       </c>
       <c r="R16" t="n">
-        <v>6708282</v>
+        <v>6708286</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,12 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129321922</v>
+        <v>129322456</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2382,39 +2377,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506804</v>
+        <v>506778</v>
       </c>
       <c r="R17" t="n">
-        <v>6708310</v>
+        <v>6708282</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2446,7 +2436,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2456,12 +2446,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2488,10 +2478,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129323053</v>
+        <v>129321922</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2499,34 +2489,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506715</v>
+        <v>506804</v>
       </c>
       <c r="R18" t="n">
-        <v>6708225</v>
+        <v>6708310</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,7 +2553,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2568,7 +2563,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,7 +2598,7 @@
         <v>129322559</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,10 +2707,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129323677</v>
+        <v>129323106</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506724</v>
+        <v>506720</v>
       </c>
       <c r="R20" t="n">
-        <v>6708250</v>
+        <v>6708241</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129323106</v>
+        <v>129323677</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506720</v>
+        <v>506724</v>
       </c>
       <c r="R21" t="n">
-        <v>6708241</v>
+        <v>6708250</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,7 +2924,7 @@
         <v>129321689</v>
       </c>
       <c r="B22" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>129322622</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>129321974</v>
       </c>
       <c r="B24" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>129323598</v>
       </c>
       <c r="B25" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3373,59 +3373,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129323359</v>
+        <v>129321706</v>
       </c>
       <c r="B26" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506713</v>
+        <v>506741</v>
       </c>
       <c r="R26" t="n">
-        <v>6708323</v>
+        <v>6708320</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3457,7 +3443,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,12 +3453,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3499,45 +3485,59 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129321706</v>
+        <v>129323359</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506741</v>
+        <v>506713</v>
       </c>
       <c r="R27" t="n">
-        <v>6708320</v>
+        <v>6708323</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3614,7 +3614,7 @@
         <v>129322464</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>129322521</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>129321673</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -1686,59 +1686,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129321663</v>
+        <v>129321725</v>
       </c>
       <c r="B11" t="n">
-        <v>98710</v>
+        <v>91543</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506726</v>
+        <v>506758</v>
       </c>
       <c r="R11" t="n">
-        <v>6708333</v>
+        <v>6708321</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,12 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ca 50+ bladrosetter, en överblommad.</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,45 +1793,59 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129321725</v>
+        <v>129321663</v>
       </c>
       <c r="B12" t="n">
-        <v>91543</v>
+        <v>98710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506758</v>
+        <v>506726</v>
       </c>
       <c r="R12" t="n">
-        <v>6708321</v>
+        <v>6708333</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,7 +1887,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 50+ bladrosetter, en överblommad.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2707,7 +2707,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129323106</v>
+        <v>129323677</v>
       </c>
       <c r="B20" t="n">
         <v>79043</v>
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506720</v>
+        <v>506724</v>
       </c>
       <c r="R20" t="n">
-        <v>6708241</v>
+        <v>6708250</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,45 +2814,59 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129323677</v>
+        <v>129321689</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>98710</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506724</v>
+        <v>506742</v>
       </c>
       <c r="R21" t="n">
-        <v>6708250</v>
+        <v>6708328</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2884,7 +2898,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2894,7 +2908,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>100+ över ca 1kvm.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2921,59 +2940,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129321689</v>
+        <v>129323106</v>
       </c>
       <c r="B22" t="n">
-        <v>98710</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506742</v>
+        <v>506720</v>
       </c>
       <c r="R22" t="n">
-        <v>6708328</v>
+        <v>6708241</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3005,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,12 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>100+ över ca 1kvm.</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129321790</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129322600</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129321919</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129322635</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>129323585</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129323568</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129323344</v>
       </c>
       <c r="B8" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>129321871</v>
       </c>
       <c r="B9" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>129323531</v>
       </c>
       <c r="B10" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,45 +1686,59 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129321725</v>
+        <v>129321663</v>
       </c>
       <c r="B11" t="n">
-        <v>91543</v>
+        <v>98712</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506758</v>
+        <v>506726</v>
       </c>
       <c r="R11" t="n">
-        <v>6708321</v>
+        <v>6708333</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1780,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca 50+ bladrosetter, en överblommad.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,59 +1812,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129321663</v>
+        <v>129321725</v>
       </c>
       <c r="B12" t="n">
-        <v>98710</v>
+        <v>91545</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506726</v>
+        <v>506758</v>
       </c>
       <c r="R12" t="n">
-        <v>6708333</v>
+        <v>6708321</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,7 +1882,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1887,12 +1892,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 50+ bladrosetter, en överblommad.</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,45 +1919,59 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129323560</v>
+        <v>129321796</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506760</v>
+        <v>506777</v>
       </c>
       <c r="R13" t="n">
-        <v>6708286</v>
+        <v>6708340</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1989,7 +2003,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1999,7 +2013,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Över knappa 1kvm, 100+.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2026,59 +2045,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129321796</v>
+        <v>129323560</v>
       </c>
       <c r="B14" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506777</v>
+        <v>506760</v>
       </c>
       <c r="R14" t="n">
-        <v>6708340</v>
+        <v>6708286</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2110,7 +2115,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2120,12 +2125,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Över knappa 1kvm, 100+.</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2155,7 +2155,7 @@
         <v>129323053</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2259,32 +2259,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129323543</v>
+        <v>129322456</v>
       </c>
       <c r="B16" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506765</v>
+        <v>506778</v>
       </c>
       <c r="R16" t="n">
-        <v>6708286</v>
+        <v>6708282</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2339,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,32 +2371,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129322456</v>
+        <v>129323543</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2401,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506778</v>
+        <v>506765</v>
       </c>
       <c r="R17" t="n">
-        <v>6708282</v>
+        <v>6708286</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2436,7 +2441,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2446,12 +2451,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2598,7 +2598,7 @@
         <v>129322559</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>129323677</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,59 +2814,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129321689</v>
+        <v>129323106</v>
       </c>
       <c r="B21" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506742</v>
+        <v>506720</v>
       </c>
       <c r="R21" t="n">
-        <v>6708328</v>
+        <v>6708241</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,7 +2884,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2908,12 +2894,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>100+ över ca 1kvm.</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,45 +2921,59 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129323106</v>
+        <v>129321689</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506720</v>
+        <v>506742</v>
       </c>
       <c r="R22" t="n">
-        <v>6708241</v>
+        <v>6708328</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3010,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3015,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>100+ över ca 1kvm.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3050,7 +3050,7 @@
         <v>129322622</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>129321974</v>
       </c>
       <c r="B24" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>129323598</v>
       </c>
       <c r="B25" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3373,45 +3373,59 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129321706</v>
+        <v>129323359</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506741</v>
+        <v>506713</v>
       </c>
       <c r="R26" t="n">
-        <v>6708320</v>
+        <v>6708323</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3443,7 +3457,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3453,12 +3467,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3485,59 +3499,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129323359</v>
+        <v>129321706</v>
       </c>
       <c r="B27" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506713</v>
+        <v>506741</v>
       </c>
       <c r="R27" t="n">
-        <v>6708323</v>
+        <v>6708320</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3614,7 +3614,7 @@
         <v>129322464</v>
       </c>
       <c r="B28" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>129322521</v>
       </c>
       <c r="B29" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>129321673</v>
       </c>
       <c r="B31" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>129321919</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129323344</v>
       </c>
       <c r="B8" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>129321871</v>
       </c>
       <c r="B9" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>129323531</v>
       </c>
       <c r="B10" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,59 +1686,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129321663</v>
+        <v>129321725</v>
       </c>
       <c r="B11" t="n">
-        <v>98712</v>
+        <v>91549</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506726</v>
+        <v>506758</v>
       </c>
       <c r="R11" t="n">
-        <v>6708333</v>
+        <v>6708321</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,12 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ca 50+ bladrosetter, en överblommad.</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,45 +1793,59 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129321725</v>
+        <v>129321663</v>
       </c>
       <c r="B12" t="n">
-        <v>91545</v>
+        <v>98716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506758</v>
+        <v>506726</v>
       </c>
       <c r="R12" t="n">
-        <v>6708321</v>
+        <v>6708333</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,7 +1887,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 50+ bladrosetter, en överblommad.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,59 +1919,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129321796</v>
+        <v>129323560</v>
       </c>
       <c r="B13" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506777</v>
+        <v>506760</v>
       </c>
       <c r="R13" t="n">
-        <v>6708340</v>
+        <v>6708286</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2003,7 +1989,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2013,12 +1999,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Över knappa 1kvm, 100+.</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,45 +2026,59 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129323560</v>
+        <v>129321796</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506760</v>
+        <v>506777</v>
       </c>
       <c r="R14" t="n">
-        <v>6708286</v>
+        <v>6708340</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2115,7 +2110,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2125,7 +2120,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Över knappa 1kvm, 100+.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2371,45 +2371,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129323543</v>
+        <v>129321922</v>
       </c>
       <c r="B17" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506765</v>
+        <v>506804</v>
       </c>
       <c r="R17" t="n">
-        <v>6708286</v>
+        <v>6708310</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2441,7 +2446,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2451,7 +2456,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2478,50 +2488,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129321922</v>
+        <v>129323543</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506804</v>
+        <v>506765</v>
       </c>
       <c r="R18" t="n">
-        <v>6708310</v>
+        <v>6708286</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2553,7 +2558,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2563,12 +2568,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2924,7 +2924,7 @@
         <v>129321689</v>
       </c>
       <c r="B22" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,45 +3047,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129322622</v>
+        <v>129321974</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506762</v>
+        <v>506804</v>
       </c>
       <c r="R23" t="n">
-        <v>6708245</v>
+        <v>6708309</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3117,7 +3121,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3131,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3136,6 +3140,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3154,49 +3159,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129321974</v>
+        <v>129322622</v>
       </c>
       <c r="B24" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506804</v>
+        <v>506762</v>
       </c>
       <c r="R24" t="n">
-        <v>6708309</v>
+        <v>6708245</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3228,7 +3229,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,7 +3239,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3247,7 +3248,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3269,7 +3269,7 @@
         <v>129323598</v>
       </c>
       <c r="B25" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3373,59 +3373,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129323359</v>
+        <v>129321706</v>
       </c>
       <c r="B26" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506713</v>
+        <v>506741</v>
       </c>
       <c r="R26" t="n">
-        <v>6708323</v>
+        <v>6708320</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3457,7 +3443,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,12 +3453,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3499,45 +3485,59 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129321706</v>
+        <v>129323359</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506741</v>
+        <v>506713</v>
       </c>
       <c r="R27" t="n">
-        <v>6708320</v>
+        <v>6708323</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>129321919</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129323344</v>
       </c>
       <c r="B8" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>129321871</v>
       </c>
       <c r="B9" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>129323531</v>
       </c>
       <c r="B10" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>129321725</v>
       </c>
       <c r="B11" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>129321663</v>
       </c>
       <c r="B12" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>129321796</v>
       </c>
       <c r="B14" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>129323543</v>
       </c>
       <c r="B18" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,45 +2707,59 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129323677</v>
+        <v>129321689</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506724</v>
+        <v>506742</v>
       </c>
       <c r="R20" t="n">
-        <v>6708250</v>
+        <v>6708328</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2777,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2801,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>100+ över ca 1kvm.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,7 +2833,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129323106</v>
+        <v>129323677</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2849,10 +2868,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506720</v>
+        <v>506724</v>
       </c>
       <c r="R21" t="n">
-        <v>6708241</v>
+        <v>6708250</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2884,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2894,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2921,59 +2940,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129321689</v>
+        <v>129323106</v>
       </c>
       <c r="B22" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506742</v>
+        <v>506720</v>
       </c>
       <c r="R22" t="n">
-        <v>6708328</v>
+        <v>6708241</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3005,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,12 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>100+ över ca 1kvm.</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3050,7 +3050,7 @@
         <v>129321974</v>
       </c>
       <c r="B23" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>129323598</v>
       </c>
       <c r="B25" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>129323359</v>
       </c>
       <c r="B27" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -1113,45 +1113,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129323585</v>
+        <v>129323344</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506744</v>
+        <v>506712</v>
       </c>
       <c r="R6" t="n">
-        <v>6708266</v>
+        <v>6708322</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1207,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>100+</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1239,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129323568</v>
+        <v>129323585</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1255,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506758</v>
+        <v>506744</v>
       </c>
       <c r="R7" t="n">
-        <v>6708281</v>
+        <v>6708266</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,59 +1346,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129323344</v>
+        <v>129323568</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506712</v>
+        <v>506758</v>
       </c>
       <c r="R8" t="n">
-        <v>6708322</v>
+        <v>6708281</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,12 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>100+</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2152,10 +2152,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129323053</v>
+        <v>129321922</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2163,34 +2163,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506715</v>
+        <v>506804</v>
       </c>
       <c r="R15" t="n">
-        <v>6708225</v>
+        <v>6708310</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2227,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2232,7 +2237,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2259,7 +2269,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129322456</v>
+        <v>129323053</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2290,14 +2300,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506778</v>
+        <v>506715</v>
       </c>
       <c r="R16" t="n">
-        <v>6708282</v>
+        <v>6708225</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,7 +2339,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,12 +2349,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,10 +2376,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129321922</v>
+        <v>129322456</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2382,39 +2387,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506804</v>
+        <v>506778</v>
       </c>
       <c r="R17" t="n">
-        <v>6708310</v>
+        <v>6708282</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2456,12 +2456,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2707,59 +2707,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129321689</v>
+        <v>129323677</v>
       </c>
       <c r="B20" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506742</v>
+        <v>506724</v>
       </c>
       <c r="R20" t="n">
-        <v>6708328</v>
+        <v>6708250</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2791,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,12 +2787,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>100+ över ca 1kvm.</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2833,7 +2814,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129323677</v>
+        <v>129323106</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2868,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506724</v>
+        <v>506720</v>
       </c>
       <c r="R21" t="n">
-        <v>6708250</v>
+        <v>6708241</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2903,7 +2884,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2913,7 +2894,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,45 +2921,59 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129323106</v>
+        <v>129321689</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506720</v>
+        <v>506742</v>
       </c>
       <c r="R22" t="n">
-        <v>6708241</v>
+        <v>6708328</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3010,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3015,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>100+ över ca 1kvm.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,49 +3047,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129321974</v>
+        <v>129322622</v>
       </c>
       <c r="B23" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506804</v>
+        <v>506762</v>
       </c>
       <c r="R23" t="n">
-        <v>6708309</v>
+        <v>6708245</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3121,7 +3117,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3131,7 +3127,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3140,7 +3136,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3159,45 +3154,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129322622</v>
+        <v>129321974</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506762</v>
+        <v>506804</v>
       </c>
       <c r="R24" t="n">
-        <v>6708245</v>
+        <v>6708309</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3229,7 +3228,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3239,7 +3238,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3248,6 +3247,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3373,45 +3373,59 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129321706</v>
+        <v>129323359</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506741</v>
+        <v>506713</v>
       </c>
       <c r="R26" t="n">
-        <v>6708320</v>
+        <v>6708323</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3443,7 +3457,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3453,12 +3467,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3485,59 +3499,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129323359</v>
+        <v>129321706</v>
       </c>
       <c r="B27" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506713</v>
+        <v>506741</v>
       </c>
       <c r="R27" t="n">
-        <v>6708323</v>
+        <v>6708320</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -1686,45 +1686,59 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129321725</v>
+        <v>129321663</v>
       </c>
       <c r="B11" t="n">
-        <v>91550</v>
+        <v>98724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506758</v>
+        <v>506726</v>
       </c>
       <c r="R11" t="n">
-        <v>6708321</v>
+        <v>6708333</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1780,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca 50+ bladrosetter, en överblommad.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,59 +1812,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129321663</v>
+        <v>129321725</v>
       </c>
       <c r="B12" t="n">
-        <v>98724</v>
+        <v>91550</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506726</v>
+        <v>506758</v>
       </c>
       <c r="R12" t="n">
-        <v>6708333</v>
+        <v>6708321</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,7 +1882,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1887,12 +1892,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 50+ bladrosetter, en överblommad.</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,45 +1919,59 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129323560</v>
+        <v>129321796</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506760</v>
+        <v>506777</v>
       </c>
       <c r="R13" t="n">
-        <v>6708286</v>
+        <v>6708340</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1989,7 +2003,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1999,7 +2013,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Över knappa 1kvm, 100+.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2026,59 +2045,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129321796</v>
+        <v>129323560</v>
       </c>
       <c r="B14" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506777</v>
+        <v>506760</v>
       </c>
       <c r="R14" t="n">
-        <v>6708340</v>
+        <v>6708286</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2110,7 +2115,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2120,12 +2125,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Över knappa 1kvm, 100+.</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2707,45 +2707,59 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129323677</v>
+        <v>129321689</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506724</v>
+        <v>506742</v>
       </c>
       <c r="R20" t="n">
-        <v>6708250</v>
+        <v>6708328</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2777,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2801,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>100+ över ca 1kvm.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,7 +2833,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129323106</v>
+        <v>129323677</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2849,10 +2868,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506720</v>
+        <v>506724</v>
       </c>
       <c r="R21" t="n">
-        <v>6708241</v>
+        <v>6708250</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2884,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2894,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2921,59 +2940,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129321689</v>
+        <v>129323106</v>
       </c>
       <c r="B22" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506742</v>
+        <v>506720</v>
       </c>
       <c r="R22" t="n">
-        <v>6708328</v>
+        <v>6708241</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3005,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,12 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>100+ över ca 1kvm.</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3373,59 +3373,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129323359</v>
+        <v>129321706</v>
       </c>
       <c r="B26" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506713</v>
+        <v>506741</v>
       </c>
       <c r="R26" t="n">
-        <v>6708323</v>
+        <v>6708320</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3457,7 +3443,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,12 +3453,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3499,45 +3485,59 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129321706</v>
+        <v>129323359</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506741</v>
+        <v>506713</v>
       </c>
       <c r="R27" t="n">
-        <v>6708320</v>
+        <v>6708323</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>129321919</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1113,59 +1113,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129323344</v>
+        <v>129323585</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506712</v>
+        <v>506744</v>
       </c>
       <c r="R6" t="n">
-        <v>6708322</v>
+        <v>6708266</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,12 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>100+</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129323585</v>
+        <v>129323568</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1274,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506744</v>
+        <v>506758</v>
       </c>
       <c r="R7" t="n">
-        <v>6708266</v>
+        <v>6708281</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,45 +1327,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129323568</v>
+        <v>129323344</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506758</v>
+        <v>506712</v>
       </c>
       <c r="R8" t="n">
-        <v>6708281</v>
+        <v>6708322</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1421,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>100+</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,7 +1456,7 @@
         <v>129321871</v>
       </c>
       <c r="B9" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>129323531</v>
       </c>
       <c r="B10" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,59 +1686,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129321663</v>
+        <v>129321725</v>
       </c>
       <c r="B11" t="n">
-        <v>98724</v>
+        <v>91553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506726</v>
+        <v>506758</v>
       </c>
       <c r="R11" t="n">
-        <v>6708333</v>
+        <v>6708321</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,12 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ca 50+ bladrosetter, en överblommad.</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,45 +1793,59 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129321725</v>
+        <v>129321663</v>
       </c>
       <c r="B12" t="n">
-        <v>91550</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506758</v>
+        <v>506726</v>
       </c>
       <c r="R12" t="n">
-        <v>6708321</v>
+        <v>6708333</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,7 +1887,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 50+ bladrosetter, en överblommad.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,7 +1922,7 @@
         <v>129321796</v>
       </c>
       <c r="B13" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2152,10 +2152,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129321922</v>
+        <v>129323053</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2163,39 +2163,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506804</v>
+        <v>506715</v>
       </c>
       <c r="R15" t="n">
-        <v>6708310</v>
+        <v>6708225</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2227,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2237,12 +2232,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2269,7 +2259,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129323053</v>
+        <v>129322456</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2300,14 +2290,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506715</v>
+        <v>506778</v>
       </c>
       <c r="R16" t="n">
-        <v>6708225</v>
+        <v>6708282</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2339,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2349,7 +2339,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2376,10 +2371,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129322456</v>
+        <v>129321922</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,34 +2382,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506778</v>
+        <v>506804</v>
       </c>
       <c r="R17" t="n">
-        <v>6708282</v>
+        <v>6708310</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2456,12 +2456,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2491,7 +2491,7 @@
         <v>129323543</v>
       </c>
       <c r="B18" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,59 +2707,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129321689</v>
+        <v>129323677</v>
       </c>
       <c r="B20" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506742</v>
+        <v>506724</v>
       </c>
       <c r="R20" t="n">
-        <v>6708328</v>
+        <v>6708250</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2791,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,12 +2787,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>100+ över ca 1kvm.</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2833,7 +2814,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129323677</v>
+        <v>129323106</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2868,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506724</v>
+        <v>506720</v>
       </c>
       <c r="R21" t="n">
-        <v>6708250</v>
+        <v>6708241</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2903,7 +2884,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2913,7 +2894,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,45 +2921,59 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129323106</v>
+        <v>129321689</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506720</v>
+        <v>506742</v>
       </c>
       <c r="R22" t="n">
-        <v>6708241</v>
+        <v>6708328</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3010,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3015,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>100+ över ca 1kvm.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3157,7 +3157,7 @@
         <v>129321974</v>
       </c>
       <c r="B24" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>129323598</v>
       </c>
       <c r="B25" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>129323359</v>
       </c>
       <c r="B27" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -2152,45 +2152,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129323053</v>
+        <v>129323543</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506715</v>
+        <v>506765</v>
       </c>
       <c r="R15" t="n">
-        <v>6708225</v>
+        <v>6708286</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2259,7 +2259,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129322456</v>
+        <v>129323053</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2290,14 +2290,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506778</v>
+        <v>506715</v>
       </c>
       <c r="R16" t="n">
-        <v>6708282</v>
+        <v>6708225</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,12 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129321922</v>
+        <v>129322456</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2382,39 +2377,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506804</v>
+        <v>506778</v>
       </c>
       <c r="R17" t="n">
-        <v>6708310</v>
+        <v>6708282</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2446,7 +2436,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2456,12 +2446,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2488,45 +2478,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129323543</v>
+        <v>129321922</v>
       </c>
       <c r="B18" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506765</v>
+        <v>506804</v>
       </c>
       <c r="R18" t="n">
-        <v>6708286</v>
+        <v>6708310</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,7 +2553,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2568,7 +2563,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2707,45 +2707,59 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129323677</v>
+        <v>129321689</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506724</v>
+        <v>506742</v>
       </c>
       <c r="R20" t="n">
-        <v>6708250</v>
+        <v>6708328</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2777,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2801,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>100+ över ca 1kvm.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2921,59 +2940,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129321689</v>
+        <v>129323677</v>
       </c>
       <c r="B22" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506742</v>
+        <v>506724</v>
       </c>
       <c r="R22" t="n">
-        <v>6708328</v>
+        <v>6708250</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3005,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,12 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>100+ över ca 1kvm.</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -2152,45 +2152,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129323543</v>
+        <v>129323053</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506765</v>
+        <v>506715</v>
       </c>
       <c r="R15" t="n">
-        <v>6708286</v>
+        <v>6708225</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2259,7 +2259,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129323053</v>
+        <v>129322456</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2290,14 +2290,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506715</v>
+        <v>506778</v>
       </c>
       <c r="R16" t="n">
-        <v>6708225</v>
+        <v>6708282</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2339,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,10 +2371,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129322456</v>
+        <v>129321922</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,34 +2382,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506778</v>
+        <v>506804</v>
       </c>
       <c r="R17" t="n">
-        <v>6708282</v>
+        <v>6708310</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2436,7 +2446,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2446,12 +2456,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2478,50 +2488,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129321922</v>
+        <v>129323543</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506804</v>
+        <v>506765</v>
       </c>
       <c r="R18" t="n">
-        <v>6708310</v>
+        <v>6708286</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2553,7 +2558,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2563,12 +2568,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2707,59 +2707,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129321689</v>
+        <v>129323677</v>
       </c>
       <c r="B20" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506742</v>
+        <v>506724</v>
       </c>
       <c r="R20" t="n">
-        <v>6708328</v>
+        <v>6708250</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2791,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,12 +2787,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>100+ över ca 1kvm.</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2940,45 +2921,59 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129323677</v>
+        <v>129321689</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506724</v>
+        <v>506742</v>
       </c>
       <c r="R22" t="n">
-        <v>6708250</v>
+        <v>6708328</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3010,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3015,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>100+ över ca 1kvm.</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -1113,45 +1113,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129323585</v>
+        <v>129323344</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506744</v>
+        <v>506712</v>
       </c>
       <c r="R6" t="n">
-        <v>6708266</v>
+        <v>6708322</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1207,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>100+</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1239,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129323568</v>
+        <v>129323585</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1255,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506758</v>
+        <v>506744</v>
       </c>
       <c r="R7" t="n">
-        <v>6708281</v>
+        <v>6708266</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,59 +1346,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129323344</v>
+        <v>129323568</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506712</v>
+        <v>506758</v>
       </c>
       <c r="R8" t="n">
-        <v>6708322</v>
+        <v>6708281</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,12 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>100+</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1686,45 +1686,59 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129321725</v>
+        <v>129321663</v>
       </c>
       <c r="B11" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506758</v>
+        <v>506726</v>
       </c>
       <c r="R11" t="n">
-        <v>6708321</v>
+        <v>6708333</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1780,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca 50+ bladrosetter, en överblommad.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,59 +1812,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129321663</v>
+        <v>129321725</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506726</v>
+        <v>506758</v>
       </c>
       <c r="R12" t="n">
-        <v>6708333</v>
+        <v>6708321</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,7 +1882,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1887,12 +1892,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 50+ bladrosetter, en överblommad.</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2152,10 +2152,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129323053</v>
+        <v>129321922</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2163,34 +2163,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506715</v>
+        <v>506804</v>
       </c>
       <c r="R15" t="n">
-        <v>6708225</v>
+        <v>6708310</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2227,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2232,7 +2237,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2259,7 +2269,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129322456</v>
+        <v>129323053</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2290,14 +2300,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506778</v>
+        <v>506715</v>
       </c>
       <c r="R16" t="n">
-        <v>6708282</v>
+        <v>6708225</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,7 +2339,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,12 +2349,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,10 +2376,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129321922</v>
+        <v>129322456</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2382,39 +2387,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506804</v>
+        <v>506778</v>
       </c>
       <c r="R17" t="n">
-        <v>6708310</v>
+        <v>6708282</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2456,12 +2456,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2707,45 +2707,59 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129323677</v>
+        <v>129321689</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506724</v>
+        <v>506742</v>
       </c>
       <c r="R20" t="n">
-        <v>6708250</v>
+        <v>6708328</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2777,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2801,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>100+ över ca 1kvm.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,7 +2833,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129323106</v>
+        <v>129323677</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2849,10 +2868,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506720</v>
+        <v>506724</v>
       </c>
       <c r="R21" t="n">
-        <v>6708241</v>
+        <v>6708250</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2884,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2894,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2921,59 +2940,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129321689</v>
+        <v>129323106</v>
       </c>
       <c r="B22" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506742</v>
+        <v>506720</v>
       </c>
       <c r="R22" t="n">
-        <v>6708328</v>
+        <v>6708241</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3005,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,12 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>100+ över ca 1kvm.</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,45 +3047,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129322622</v>
+        <v>129321974</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506762</v>
+        <v>506804</v>
       </c>
       <c r="R23" t="n">
-        <v>6708245</v>
+        <v>6708309</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3117,7 +3121,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3131,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3136,6 +3140,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3154,49 +3159,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129321974</v>
+        <v>129322622</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506804</v>
+        <v>506762</v>
       </c>
       <c r="R24" t="n">
-        <v>6708309</v>
+        <v>6708245</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3228,7 +3229,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,7 +3239,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3247,7 +3248,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -1113,59 +1113,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129323344</v>
+        <v>129323585</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506712</v>
+        <v>506744</v>
       </c>
       <c r="R6" t="n">
-        <v>6708322</v>
+        <v>6708266</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,12 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>100+</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129323585</v>
+        <v>129323568</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1274,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506744</v>
+        <v>506758</v>
       </c>
       <c r="R7" t="n">
-        <v>6708266</v>
+        <v>6708281</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,45 +1327,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129323568</v>
+        <v>129323344</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506758</v>
+        <v>506712</v>
       </c>
       <c r="R8" t="n">
-        <v>6708281</v>
+        <v>6708322</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1421,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>100+</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2152,50 +2152,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129321922</v>
+        <v>129323543</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506804</v>
+        <v>506765</v>
       </c>
       <c r="R15" t="n">
-        <v>6708310</v>
+        <v>6708286</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2227,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2237,12 +2232,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2269,7 +2259,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129323053</v>
+        <v>129322456</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2300,14 +2290,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506715</v>
+        <v>506778</v>
       </c>
       <c r="R16" t="n">
-        <v>6708225</v>
+        <v>6708282</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2339,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2349,7 +2339,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2376,7 +2371,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129322456</v>
+        <v>129323053</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2407,14 +2402,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506778</v>
+        <v>506715</v>
       </c>
       <c r="R17" t="n">
-        <v>6708282</v>
+        <v>6708225</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2446,7 +2441,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2456,12 +2451,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2488,45 +2478,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129323543</v>
+        <v>129321922</v>
       </c>
       <c r="B18" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506765</v>
+        <v>506804</v>
       </c>
       <c r="R18" t="n">
-        <v>6708286</v>
+        <v>6708310</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,7 +2553,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2568,7 +2563,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2707,59 +2707,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129321689</v>
+        <v>129323677</v>
       </c>
       <c r="B20" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506742</v>
+        <v>506724</v>
       </c>
       <c r="R20" t="n">
-        <v>6708328</v>
+        <v>6708250</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2791,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,12 +2787,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>100+ över ca 1kvm.</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2833,7 +2814,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129323677</v>
+        <v>129323106</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2868,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506724</v>
+        <v>506720</v>
       </c>
       <c r="R21" t="n">
-        <v>6708250</v>
+        <v>6708241</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2903,7 +2884,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2913,7 +2894,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,45 +2921,59 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129323106</v>
+        <v>129321689</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506720</v>
+        <v>506742</v>
       </c>
       <c r="R22" t="n">
-        <v>6708241</v>
+        <v>6708328</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3010,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3015,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>100+ över ca 1kvm.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,49 +3047,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129321974</v>
+        <v>129322622</v>
       </c>
       <c r="B23" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506804</v>
+        <v>506762</v>
       </c>
       <c r="R23" t="n">
-        <v>6708309</v>
+        <v>6708245</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3121,7 +3117,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3131,7 +3127,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3140,7 +3136,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3159,45 +3154,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129322622</v>
+        <v>129321974</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506762</v>
+        <v>506804</v>
       </c>
       <c r="R24" t="n">
-        <v>6708245</v>
+        <v>6708309</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3229,7 +3228,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3239,7 +3238,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3248,6 +3247,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3373,45 +3373,59 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129321706</v>
+        <v>129323359</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506741</v>
+        <v>506713</v>
       </c>
       <c r="R26" t="n">
-        <v>6708320</v>
+        <v>6708323</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3443,7 +3457,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3453,12 +3467,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3485,59 +3499,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129323359</v>
+        <v>129321706</v>
       </c>
       <c r="B27" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506713</v>
+        <v>506741</v>
       </c>
       <c r="R27" t="n">
-        <v>6708323</v>
+        <v>6708320</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129322600</v>
+        <v>129321919</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506762</v>
+        <v>506804</v>
       </c>
       <c r="R3" t="n">
-        <v>6708250</v>
+        <v>6708310</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129321919</v>
+        <v>129322600</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506804</v>
+        <v>506762</v>
       </c>
       <c r="R4" t="n">
-        <v>6708310</v>
+        <v>6708250</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1113,45 +1113,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129323585</v>
+        <v>129323344</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506744</v>
+        <v>506712</v>
       </c>
       <c r="R6" t="n">
-        <v>6708266</v>
+        <v>6708322</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1207,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>100+</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1239,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129323568</v>
+        <v>129323585</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1255,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506758</v>
+        <v>506744</v>
       </c>
       <c r="R7" t="n">
-        <v>6708281</v>
+        <v>6708266</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,59 +1346,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129323344</v>
+        <v>129323568</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506712</v>
+        <v>506758</v>
       </c>
       <c r="R8" t="n">
-        <v>6708322</v>
+        <v>6708281</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,12 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>100+</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1919,59 +1919,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129321796</v>
+        <v>129323560</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506777</v>
+        <v>506760</v>
       </c>
       <c r="R13" t="n">
-        <v>6708340</v>
+        <v>6708286</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2003,7 +1989,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2013,12 +1999,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Över knappa 1kvm, 100+.</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,45 +2026,59 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129323560</v>
+        <v>129321796</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506760</v>
+        <v>506777</v>
       </c>
       <c r="R14" t="n">
-        <v>6708286</v>
+        <v>6708340</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2115,7 +2110,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2125,7 +2120,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Över knappa 1kvm, 100+.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2152,45 +2152,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129323543</v>
+        <v>129323053</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506765</v>
+        <v>506715</v>
       </c>
       <c r="R15" t="n">
-        <v>6708286</v>
+        <v>6708225</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2371,10 +2371,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129323053</v>
+        <v>129321922</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2382,34 +2382,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506715</v>
+        <v>506804</v>
       </c>
       <c r="R17" t="n">
-        <v>6708225</v>
+        <v>6708310</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2441,7 +2446,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2451,7 +2456,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2478,50 +2488,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129321922</v>
+        <v>129323543</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506804</v>
+        <v>506765</v>
       </c>
       <c r="R18" t="n">
-        <v>6708310</v>
+        <v>6708286</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2553,7 +2558,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2563,12 +2568,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3047,45 +3047,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129322622</v>
+        <v>129321974</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506762</v>
+        <v>506804</v>
       </c>
       <c r="R23" t="n">
-        <v>6708245</v>
+        <v>6708309</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3117,7 +3121,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3131,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3136,6 +3140,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3154,49 +3159,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129321974</v>
+        <v>129322622</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506804</v>
+        <v>506762</v>
       </c>
       <c r="R24" t="n">
-        <v>6708309</v>
+        <v>6708245</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3228,7 +3229,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,7 +3239,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3247,7 +3248,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3373,59 +3373,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129323359</v>
+        <v>129321706</v>
       </c>
       <c r="B26" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506713</v>
+        <v>506741</v>
       </c>
       <c r="R26" t="n">
-        <v>6708323</v>
+        <v>6708320</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3457,7 +3443,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,12 +3453,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3499,45 +3485,59 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129321706</v>
+        <v>129323359</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506741</v>
+        <v>506713</v>
       </c>
       <c r="R27" t="n">
-        <v>6708320</v>
+        <v>6708323</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129321790</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129321919</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129322600</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129322635</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,59 +1113,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129323344</v>
+        <v>129323585</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506712</v>
+        <v>506744</v>
       </c>
       <c r="R6" t="n">
-        <v>6708322</v>
+        <v>6708266</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,12 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>100+</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129323585</v>
+        <v>129323568</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506744</v>
+        <v>506758</v>
       </c>
       <c r="R7" t="n">
-        <v>6708266</v>
+        <v>6708281</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,45 +1327,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129323568</v>
+        <v>129323344</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506758</v>
+        <v>506712</v>
       </c>
       <c r="R8" t="n">
-        <v>6708281</v>
+        <v>6708322</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1421,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>100+</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,7 +1456,7 @@
         <v>129321871</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>129323531</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,59 +1686,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129321663</v>
+        <v>129321725</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>91581</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506726</v>
+        <v>506758</v>
       </c>
       <c r="R11" t="n">
-        <v>6708333</v>
+        <v>6708321</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,12 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ca 50+ bladrosetter, en överblommad.</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,45 +1793,59 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129321725</v>
+        <v>129321663</v>
       </c>
       <c r="B12" t="n">
-        <v>91553</v>
+        <v>98756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506758</v>
+        <v>506726</v>
       </c>
       <c r="R12" t="n">
-        <v>6708321</v>
+        <v>6708333</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,7 +1887,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 50+ bladrosetter, en överblommad.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,7 +1922,7 @@
         <v>129323560</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>129321796</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>129323053</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>129322456</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2371,50 +2371,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129321922</v>
+        <v>129323543</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>98756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506804</v>
+        <v>506765</v>
       </c>
       <c r="R17" t="n">
-        <v>6708310</v>
+        <v>6708286</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2446,7 +2441,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2456,12 +2451,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2488,45 +2478,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129323543</v>
+        <v>129321922</v>
       </c>
       <c r="B18" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506765</v>
+        <v>506804</v>
       </c>
       <c r="R18" t="n">
-        <v>6708286</v>
+        <v>6708310</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,7 +2553,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2568,7 +2563,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,7 +2598,7 @@
         <v>129322559</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>129323677</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>129323106</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>129321689</v>
       </c>
       <c r="B22" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,49 +3047,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129321974</v>
+        <v>129322622</v>
       </c>
       <c r="B23" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506804</v>
+        <v>506762</v>
       </c>
       <c r="R23" t="n">
-        <v>6708309</v>
+        <v>6708245</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3121,7 +3117,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3131,7 +3127,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3140,7 +3136,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3159,45 +3154,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129322622</v>
+        <v>129321974</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506762</v>
+        <v>506804</v>
       </c>
       <c r="R24" t="n">
-        <v>6708245</v>
+        <v>6708309</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3229,7 +3228,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3239,7 +3238,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3248,6 +3247,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3269,7 +3269,7 @@
         <v>129323598</v>
       </c>
       <c r="B25" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3373,45 +3373,59 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129321706</v>
+        <v>129323359</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506741</v>
+        <v>506713</v>
       </c>
       <c r="R26" t="n">
-        <v>6708320</v>
+        <v>6708323</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3443,7 +3457,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3453,12 +3467,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3485,59 +3499,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129323359</v>
+        <v>129321706</v>
       </c>
       <c r="B27" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506713</v>
+        <v>506741</v>
       </c>
       <c r="R27" t="n">
-        <v>6708323</v>
+        <v>6708320</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3614,7 +3614,7 @@
         <v>129322464</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>129322521</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>129322534</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>129321673</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129321790</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129321919</v>
+        <v>129322600</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506804</v>
+        <v>506762</v>
       </c>
       <c r="R3" t="n">
-        <v>6708310</v>
+        <v>6708250</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129322600</v>
+        <v>129321919</v>
       </c>
       <c r="B4" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506762</v>
+        <v>506804</v>
       </c>
       <c r="R4" t="n">
-        <v>6708250</v>
+        <v>6708310</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,12 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1009,7 @@
         <v>129322635</v>
       </c>
       <c r="B5" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129323585</v>
+        <v>129323568</v>
       </c>
       <c r="B6" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506744</v>
+        <v>506758</v>
       </c>
       <c r="R6" t="n">
-        <v>6708266</v>
+        <v>6708281</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129323568</v>
+        <v>129323585</v>
       </c>
       <c r="B7" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506758</v>
+        <v>506744</v>
       </c>
       <c r="R7" t="n">
-        <v>6708281</v>
+        <v>6708266</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,7 +1330,7 @@
         <v>129323344</v>
       </c>
       <c r="B8" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>129321871</v>
       </c>
       <c r="B9" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>129323531</v>
       </c>
       <c r="B10" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>129321725</v>
       </c>
       <c r="B11" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>129321663</v>
       </c>
       <c r="B12" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>129323560</v>
       </c>
       <c r="B13" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>129321796</v>
       </c>
       <c r="B14" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,10 +2152,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129323053</v>
+        <v>129321922</v>
       </c>
       <c r="B15" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2163,34 +2163,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506715</v>
+        <v>506804</v>
       </c>
       <c r="R15" t="n">
-        <v>6708225</v>
+        <v>6708310</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2227,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2232,7 +2237,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2259,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129322456</v>
+        <v>129323053</v>
       </c>
       <c r="B16" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2290,14 +2300,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506778</v>
+        <v>506715</v>
       </c>
       <c r="R16" t="n">
-        <v>6708282</v>
+        <v>6708225</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,7 +2339,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,12 +2349,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,32 +2376,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129323543</v>
+        <v>129322456</v>
       </c>
       <c r="B17" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2406,10 +2411,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506765</v>
+        <v>506778</v>
       </c>
       <c r="R17" t="n">
-        <v>6708286</v>
+        <v>6708282</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2441,7 +2446,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2451,7 +2456,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2478,50 +2488,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129321922</v>
+        <v>129323543</v>
       </c>
       <c r="B18" t="n">
-        <v>57730</v>
+        <v>98768</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506804</v>
+        <v>506765</v>
       </c>
       <c r="R18" t="n">
-        <v>6708310</v>
+        <v>6708286</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2553,7 +2558,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2563,12 +2568,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,7 +2598,7 @@
         <v>129322559</v>
       </c>
       <c r="B19" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,10 +2707,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129323677</v>
+        <v>129323106</v>
       </c>
       <c r="B20" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506724</v>
+        <v>506720</v>
       </c>
       <c r="R20" t="n">
-        <v>6708250</v>
+        <v>6708241</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,45 +2814,59 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129323106</v>
+        <v>129321689</v>
       </c>
       <c r="B21" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506720</v>
+        <v>506742</v>
       </c>
       <c r="R21" t="n">
-        <v>6708241</v>
+        <v>6708328</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2884,7 +2898,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2894,7 +2908,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>100+ över ca 1kvm.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2921,59 +2940,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129321689</v>
+        <v>129323677</v>
       </c>
       <c r="B22" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506742</v>
+        <v>506724</v>
       </c>
       <c r="R22" t="n">
-        <v>6708328</v>
+        <v>6708250</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3005,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,12 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>100+ över ca 1kvm.</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3050,7 +3050,7 @@
         <v>129322622</v>
       </c>
       <c r="B23" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>129321974</v>
       </c>
       <c r="B24" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>129323598</v>
       </c>
       <c r="B25" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3373,59 +3373,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129323359</v>
+        <v>129321706</v>
       </c>
       <c r="B26" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506713</v>
+        <v>506741</v>
       </c>
       <c r="R26" t="n">
-        <v>6708323</v>
+        <v>6708320</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3457,7 +3443,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,12 +3453,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3499,45 +3485,59 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129321706</v>
+        <v>129323359</v>
       </c>
       <c r="B27" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506741</v>
+        <v>506713</v>
       </c>
       <c r="R27" t="n">
-        <v>6708320</v>
+        <v>6708323</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3614,7 +3614,7 @@
         <v>129322464</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>129322521</v>
       </c>
       <c r="B29" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>129322534</v>
       </c>
       <c r="B30" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>129321673</v>
       </c>
       <c r="B31" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129321790</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129322600</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129321919</v>
       </c>
       <c r="B4" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129322635</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129323568</v>
+        <v>129323585</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506758</v>
+        <v>506744</v>
       </c>
       <c r="R6" t="n">
-        <v>6708281</v>
+        <v>6708266</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,45 +1220,59 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129323585</v>
+        <v>129323344</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506744</v>
+        <v>506712</v>
       </c>
       <c r="R7" t="n">
-        <v>6708266</v>
+        <v>6708322</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1314,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>100+</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,59 +1346,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129323344</v>
+        <v>129323568</v>
       </c>
       <c r="B8" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506712</v>
+        <v>506758</v>
       </c>
       <c r="R8" t="n">
-        <v>6708322</v>
+        <v>6708281</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,12 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>100+</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,7 +1456,7 @@
         <v>129321871</v>
       </c>
       <c r="B9" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>129323531</v>
       </c>
       <c r="B10" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,45 +1686,59 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129321725</v>
+        <v>129321663</v>
       </c>
       <c r="B11" t="n">
-        <v>91587</v>
+        <v>98769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506758</v>
+        <v>506726</v>
       </c>
       <c r="R11" t="n">
-        <v>6708321</v>
+        <v>6708333</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1780,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca 50+ bladrosetter, en överblommad.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,59 +1812,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129321663</v>
+        <v>129321725</v>
       </c>
       <c r="B12" t="n">
-        <v>98768</v>
+        <v>91588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506726</v>
+        <v>506758</v>
       </c>
       <c r="R12" t="n">
-        <v>6708333</v>
+        <v>6708321</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,7 +1882,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1887,12 +1892,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 50+ bladrosetter, en överblommad.</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,7 +1922,7 @@
         <v>129323560</v>
       </c>
       <c r="B13" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>129321796</v>
       </c>
       <c r="B14" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,10 +2152,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129321922</v>
+        <v>129323053</v>
       </c>
       <c r="B15" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2163,39 +2163,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506804</v>
+        <v>506715</v>
       </c>
       <c r="R15" t="n">
-        <v>6708310</v>
+        <v>6708225</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2227,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2237,12 +2232,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2269,45 +2259,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129323053</v>
+        <v>129323543</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506715</v>
+        <v>506765</v>
       </c>
       <c r="R16" t="n">
-        <v>6708225</v>
+        <v>6708286</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2339,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2349,7 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2379,7 +2369,7 @@
         <v>129322456</v>
       </c>
       <c r="B17" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2488,45 +2478,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129323543</v>
+        <v>129321922</v>
       </c>
       <c r="B18" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506765</v>
+        <v>506804</v>
       </c>
       <c r="R18" t="n">
-        <v>6708286</v>
+        <v>6708310</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,7 +2553,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2568,7 +2563,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,7 +2598,7 @@
         <v>129322559</v>
       </c>
       <c r="B19" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,45 +2707,59 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129323106</v>
+        <v>129321689</v>
       </c>
       <c r="B20" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506720</v>
+        <v>506742</v>
       </c>
       <c r="R20" t="n">
-        <v>6708241</v>
+        <v>6708328</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2777,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2801,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>100+ över ca 1kvm.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,59 +2833,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129321689</v>
+        <v>129323677</v>
       </c>
       <c r="B21" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506742</v>
+        <v>506724</v>
       </c>
       <c r="R21" t="n">
-        <v>6708328</v>
+        <v>6708250</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2908,12 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>100+ över ca 1kvm.</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,10 +2940,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129323677</v>
+        <v>129323106</v>
       </c>
       <c r="B22" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506724</v>
+        <v>506720</v>
       </c>
       <c r="R22" t="n">
-        <v>6708250</v>
+        <v>6708241</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3050,7 +3050,7 @@
         <v>129322622</v>
       </c>
       <c r="B23" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>129321974</v>
       </c>
       <c r="B24" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>129323598</v>
       </c>
       <c r="B25" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3373,45 +3373,59 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129321706</v>
+        <v>129323359</v>
       </c>
       <c r="B26" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506741</v>
+        <v>506713</v>
       </c>
       <c r="R26" t="n">
-        <v>6708320</v>
+        <v>6708323</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3443,7 +3457,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3453,12 +3467,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3485,59 +3499,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129323359</v>
+        <v>129321706</v>
       </c>
       <c r="B27" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506713</v>
+        <v>506741</v>
       </c>
       <c r="R27" t="n">
-        <v>6708323</v>
+        <v>6708320</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3614,7 +3614,7 @@
         <v>129322464</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>129322521</v>
       </c>
       <c r="B29" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>129322534</v>
       </c>
       <c r="B30" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>129321673</v>
       </c>
       <c r="B31" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -1220,59 +1220,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129323344</v>
+        <v>129323568</v>
       </c>
       <c r="B7" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506712</v>
+        <v>506758</v>
       </c>
       <c r="R7" t="n">
-        <v>6708322</v>
+        <v>6708281</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,12 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>100+</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,45 +1327,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129323568</v>
+        <v>129323344</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>98769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506758</v>
+        <v>506712</v>
       </c>
       <c r="R8" t="n">
-        <v>6708281</v>
+        <v>6708322</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1421,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>100+</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1686,59 +1686,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129321663</v>
+        <v>129321725</v>
       </c>
       <c r="B11" t="n">
-        <v>98769</v>
+        <v>91588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506726</v>
+        <v>506758</v>
       </c>
       <c r="R11" t="n">
-        <v>6708333</v>
+        <v>6708321</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,12 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ca 50+ bladrosetter, en överblommad.</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,45 +1793,59 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129321725</v>
+        <v>129321663</v>
       </c>
       <c r="B12" t="n">
-        <v>91588</v>
+        <v>98769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506758</v>
+        <v>506726</v>
       </c>
       <c r="R12" t="n">
-        <v>6708321</v>
+        <v>6708333</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,7 +1887,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 50+ bladrosetter, en överblommad.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -3373,59 +3373,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129323359</v>
+        <v>129321706</v>
       </c>
       <c r="B26" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506713</v>
+        <v>506741</v>
       </c>
       <c r="R26" t="n">
-        <v>6708323</v>
+        <v>6708320</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3457,7 +3443,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,12 +3453,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3499,45 +3485,59 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129321706</v>
+        <v>129323359</v>
       </c>
       <c r="B27" t="n">
-        <v>79076</v>
+        <v>98769</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506741</v>
+        <v>506713</v>
       </c>
       <c r="R27" t="n">
-        <v>6708320</v>
+        <v>6708323</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129321790</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129322600</v>
+        <v>129321919</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506762</v>
+        <v>506804</v>
       </c>
       <c r="R3" t="n">
-        <v>6708250</v>
+        <v>6708310</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129321919</v>
+        <v>129322600</v>
       </c>
       <c r="B4" t="n">
-        <v>98769</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506804</v>
+        <v>506762</v>
       </c>
       <c r="R4" t="n">
-        <v>6708310</v>
+        <v>6708250</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1009,7 @@
         <v>129322635</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>129323585</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129323568</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129323344</v>
       </c>
       <c r="B8" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>129321871</v>
       </c>
       <c r="B9" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>129323531</v>
       </c>
       <c r="B10" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,45 +1686,59 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129321725</v>
+        <v>129321663</v>
       </c>
       <c r="B11" t="n">
-        <v>91588</v>
+        <v>98774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506758</v>
+        <v>506726</v>
       </c>
       <c r="R11" t="n">
-        <v>6708321</v>
+        <v>6708333</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1780,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca 50+ bladrosetter, en överblommad.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,59 +1812,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129321663</v>
+        <v>129321725</v>
       </c>
       <c r="B12" t="n">
-        <v>98769</v>
+        <v>91593</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506726</v>
+        <v>506758</v>
       </c>
       <c r="R12" t="n">
-        <v>6708333</v>
+        <v>6708321</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,7 +1882,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1887,12 +1892,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 50+ bladrosetter, en överblommad.</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,7 +1922,7 @@
         <v>129323560</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>129321796</v>
       </c>
       <c r="B14" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,45 +2152,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129323053</v>
+        <v>129323543</v>
       </c>
       <c r="B15" t="n">
-        <v>79076</v>
+        <v>98774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506715</v>
+        <v>506765</v>
       </c>
       <c r="R15" t="n">
-        <v>6708225</v>
+        <v>6708286</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2259,45 +2259,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129323543</v>
+        <v>129323053</v>
       </c>
       <c r="B16" t="n">
-        <v>98769</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506765</v>
+        <v>506715</v>
       </c>
       <c r="R16" t="n">
-        <v>6708286</v>
+        <v>6708225</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2369,7 +2369,7 @@
         <v>129322456</v>
       </c>
       <c r="B17" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>129322559</v>
       </c>
       <c r="B19" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>129321689</v>
       </c>
       <c r="B20" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>129323677</v>
       </c>
       <c r="B21" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>129323106</v>
       </c>
       <c r="B22" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>129322622</v>
       </c>
       <c r="B23" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>129321974</v>
       </c>
       <c r="B24" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>129323598</v>
       </c>
       <c r="B25" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>129321706</v>
       </c>
       <c r="B26" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>129323359</v>
       </c>
       <c r="B27" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>129322464</v>
       </c>
       <c r="B28" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>129322521</v>
       </c>
       <c r="B29" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>129321673</v>
       </c>
       <c r="B31" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129321919</v>
+        <v>129322600</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506804</v>
+        <v>506762</v>
       </c>
       <c r="R3" t="n">
-        <v>6708310</v>
+        <v>6708250</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129322600</v>
+        <v>129321919</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506762</v>
+        <v>506804</v>
       </c>
       <c r="R4" t="n">
-        <v>6708250</v>
+        <v>6708310</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,12 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1113,45 +1113,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129323585</v>
+        <v>129323344</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506744</v>
+        <v>506712</v>
       </c>
       <c r="R6" t="n">
-        <v>6708266</v>
+        <v>6708322</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1207,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>100+</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1239,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129323568</v>
+        <v>129323585</v>
       </c>
       <c r="B7" t="n">
         <v>79081</v>
@@ -1255,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506758</v>
+        <v>506744</v>
       </c>
       <c r="R7" t="n">
-        <v>6708281</v>
+        <v>6708266</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,59 +1346,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129323344</v>
+        <v>129323568</v>
       </c>
       <c r="B8" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506712</v>
+        <v>506758</v>
       </c>
       <c r="R8" t="n">
-        <v>6708322</v>
+        <v>6708281</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,12 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>100+</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1919,45 +1919,59 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129323560</v>
+        <v>129321796</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506760</v>
+        <v>506777</v>
       </c>
       <c r="R13" t="n">
-        <v>6708286</v>
+        <v>6708340</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1989,7 +2003,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1999,7 +2013,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Över knappa 1kvm, 100+.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2026,59 +2045,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129321796</v>
+        <v>129323560</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506777</v>
+        <v>506760</v>
       </c>
       <c r="R14" t="n">
-        <v>6708340</v>
+        <v>6708286</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2110,7 +2115,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2120,12 +2125,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Över knappa 1kvm, 100+.</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2707,59 +2707,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129321689</v>
+        <v>129323677</v>
       </c>
       <c r="B20" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506742</v>
+        <v>506724</v>
       </c>
       <c r="R20" t="n">
-        <v>6708328</v>
+        <v>6708250</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2791,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,12 +2787,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>100+ över ca 1kvm.</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2833,45 +2814,59 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129323677</v>
+        <v>129321689</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506724</v>
+        <v>506742</v>
       </c>
       <c r="R21" t="n">
-        <v>6708250</v>
+        <v>6708328</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2903,7 +2898,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2913,7 +2908,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>100+ över ca 1kvm.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3373,45 +3373,59 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129321706</v>
+        <v>129323359</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506741</v>
+        <v>506713</v>
       </c>
       <c r="R26" t="n">
-        <v>6708320</v>
+        <v>6708323</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3443,7 +3457,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3453,12 +3467,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3485,59 +3499,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129323359</v>
+        <v>129321706</v>
       </c>
       <c r="B27" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506713</v>
+        <v>506741</v>
       </c>
       <c r="R27" t="n">
-        <v>6708323</v>
+        <v>6708320</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129321790</v>
+        <v>129321725</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506777</v>
+        <v>506758</v>
       </c>
       <c r="R2" t="n">
-        <v>6708340</v>
+        <v>6708321</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,14 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129322600</v>
+        <v>129321445</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506762</v>
+        <v>506645</v>
       </c>
       <c r="R3" t="n">
-        <v>6708250</v>
+        <v>6708359</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129321919</v>
+        <v>129321451</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506804</v>
+        <v>506645</v>
       </c>
       <c r="R4" t="n">
-        <v>6708310</v>
+        <v>6708357</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,14 +996,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129322635</v>
+        <v>129321673</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1037,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506758</v>
+        <v>506735</v>
       </c>
       <c r="R5" t="n">
-        <v>6708237</v>
+        <v>6708332</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1076,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129323344</v>
+        <v>129321706</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,48 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506712</v>
+        <v>506741</v>
       </c>
       <c r="R6" t="n">
-        <v>6708322</v>
+        <v>6708320</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,12 +1188,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>100+</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,14 +1220,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129323585</v>
+        <v>129321790</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1274,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506744</v>
+        <v>506777</v>
       </c>
       <c r="R7" t="n">
-        <v>6708266</v>
+        <v>6708340</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1300,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,14 +1332,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129323568</v>
+        <v>129322151</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1381,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506758</v>
+        <v>506831</v>
       </c>
       <c r="R8" t="n">
-        <v>6708281</v>
+        <v>6708322</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1412,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129321871</v>
+        <v>129322456</v>
       </c>
       <c r="B9" t="n">
-        <v>98774</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,48 +1455,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506794</v>
+        <v>506778</v>
       </c>
       <c r="R9" t="n">
-        <v>6708308</v>
+        <v>6708282</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,12 +1524,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Över ca 1kvm, rikligt, 150+.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129323531</v>
+        <v>129322464</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1590,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1614,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506781</v>
+        <v>506779</v>
       </c>
       <c r="R10" t="n">
-        <v>6708313</v>
+        <v>6708280</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,7 +1626,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1636,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129321663</v>
+        <v>129322521</v>
       </c>
       <c r="B11" t="n">
-        <v>98774</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,48 +1679,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506726</v>
+        <v>506769</v>
       </c>
       <c r="R11" t="n">
-        <v>6708333</v>
+        <v>6708266</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,7 +1738,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,12 +1748,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ca 50+ bladrosetter, en överblommad.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,32 +1780,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129321725</v>
+        <v>129322559</v>
       </c>
       <c r="B12" t="n">
-        <v>91593</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1847,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506758</v>
+        <v>506760</v>
       </c>
       <c r="R12" t="n">
-        <v>6708321</v>
+        <v>6708246</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,7 +1850,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,7 +1860,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129321796</v>
+        <v>129322600</v>
       </c>
       <c r="B13" t="n">
-        <v>98774</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1930,48 +1903,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506777</v>
+        <v>506762</v>
       </c>
       <c r="R13" t="n">
-        <v>6708340</v>
+        <v>6708250</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2003,7 +1962,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2013,12 +1972,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Över knappa 1kvm, 100+.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,14 +2004,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129323560</v>
+        <v>129322622</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2076,14 +2035,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506760</v>
+        <v>506762</v>
       </c>
       <c r="R14" t="n">
-        <v>6708286</v>
+        <v>6708245</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2115,7 +2074,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2125,7 +2084,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2152,10 +2111,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129323543</v>
+        <v>129322635</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2163,34 +2122,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506765</v>
+        <v>506758</v>
       </c>
       <c r="R15" t="n">
-        <v>6708286</v>
+        <v>6708237</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2181,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2232,7 +2191,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2259,14 +2218,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129323053</v>
+        <v>129322990</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2294,10 +2253,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506715</v>
+        <v>506692</v>
       </c>
       <c r="R16" t="n">
-        <v>6708225</v>
+        <v>6708210</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,7 +2288,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2298,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,14 +2325,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129322456</v>
+        <v>129323037</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2397,14 +2356,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506778</v>
+        <v>506700</v>
       </c>
       <c r="R17" t="n">
-        <v>6708282</v>
+        <v>6708219</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2436,7 +2395,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2446,12 +2405,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2478,50 +2432,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129321922</v>
+        <v>129323053</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506804</v>
+        <v>506715</v>
       </c>
       <c r="R18" t="n">
-        <v>6708310</v>
+        <v>6708225</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2553,7 +2502,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2563,12 +2512,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2595,14 +2539,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129322559</v>
+        <v>129323106</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2626,14 +2570,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506760</v>
+        <v>506720</v>
       </c>
       <c r="R19" t="n">
-        <v>6708246</v>
+        <v>6708241</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2665,7 +2609,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2675,12 +2619,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2707,14 +2646,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129323677</v>
+        <v>129323560</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2738,14 +2677,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506724</v>
+        <v>506760</v>
       </c>
       <c r="R20" t="n">
-        <v>6708250</v>
+        <v>6708286</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2777,7 +2716,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2726,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,10 +2753,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129321689</v>
+        <v>129323568</v>
       </c>
       <c r="B21" t="n">
-        <v>98774</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,48 +2764,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506742</v>
+        <v>506758</v>
       </c>
       <c r="R21" t="n">
-        <v>6708328</v>
+        <v>6708281</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,7 +2823,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2908,12 +2833,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>100+ över ca 1kvm.</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,14 +2860,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129323106</v>
+        <v>129323585</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2971,14 +2891,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506720</v>
+        <v>506744</v>
       </c>
       <c r="R22" t="n">
-        <v>6708241</v>
+        <v>6708266</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3010,7 +2930,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +2940,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,14 +2967,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129322622</v>
+        <v>129323677</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3082,10 +3002,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506762</v>
+        <v>506724</v>
       </c>
       <c r="R23" t="n">
-        <v>6708245</v>
+        <v>6708250</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3117,7 +3037,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3047,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3154,39 +3074,40 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129321974</v>
+        <v>129321922</v>
       </c>
       <c r="B24" t="n">
-        <v>98774</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
@@ -3196,7 +3117,7 @@
         <v>506804</v>
       </c>
       <c r="R24" t="n">
-        <v>6708309</v>
+        <v>6708310</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3228,7 +3149,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,7 +3159,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3247,7 +3173,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3266,45 +3191,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129323598</v>
+        <v>129322534</v>
       </c>
       <c r="B25" t="n">
-        <v>98774</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506737</v>
+        <v>506774</v>
       </c>
       <c r="R25" t="n">
-        <v>6708251</v>
+        <v>6708265</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3336,7 +3266,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,7 +3276,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre och färska.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3373,47 +3308,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129323359</v>
+        <v>129322346</v>
       </c>
       <c r="B26" t="n">
-        <v>98774</v>
+        <v>5179</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3422,10 +3348,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506713</v>
+        <v>506824</v>
       </c>
       <c r="R26" t="n">
-        <v>6708323</v>
+        <v>6708300</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3457,7 +3383,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,19 +3393,14 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG26" t="b">
         <v>0</v>
@@ -3499,10 +3420,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129321706</v>
+        <v>129322929</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>58114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,34 +3431,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506741</v>
+        <v>506716</v>
       </c>
       <c r="R27" t="n">
-        <v>6708320</v>
+        <v>6708206</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3569,7 +3495,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,12 +3505,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3611,45 +3532,59 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129322464</v>
+        <v>129321663</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506779</v>
+        <v>506726</v>
       </c>
       <c r="R28" t="n">
-        <v>6708280</v>
+        <v>6708333</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3681,7 +3616,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3691,12 +3626,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ca 50+ bladrosetter, en överblommad.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3723,45 +3658,59 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129322521</v>
+        <v>129321689</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506769</v>
+        <v>506742</v>
       </c>
       <c r="R29" t="n">
-        <v>6708266</v>
+        <v>6708328</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3793,7 +3742,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3803,12 +3752,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>100+ över ca 1kvm.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3835,38 +3784,47 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129322534</v>
+        <v>129321796</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3875,10 +3833,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506774</v>
+        <v>506777</v>
       </c>
       <c r="R30" t="n">
-        <v>6708265</v>
+        <v>6708340</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3910,7 +3868,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3920,12 +3878,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre och färska.</t>
+          <t>Över knappa 1kvm, 100+.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3952,45 +3910,59 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129321673</v>
+        <v>129321871</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506735</v>
+        <v>506794</v>
       </c>
       <c r="R31" t="n">
-        <v>6708332</v>
+        <v>6708308</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4022,7 +3994,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4032,12 +4004,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Över ca 1kvm, rikligt, 150+.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4061,6 +4033,798 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129321919</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>506804</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6708310</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129321974</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>506804</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6708309</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129323344</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>506712</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6708322</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129323359</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>506713</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6708323</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129323531</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>506781</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6708313</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129323543</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Dammyrbäcken, Dammyrbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>506765</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6708286</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129323598</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Gettjärnsmoren, Gettjärnsmoren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>506737</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6708251</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51268-2025 artfynd.xlsx
+++ b/artfynd/A 51268-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129321725</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129321445</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129321451</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129321673</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129321706</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129321790</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129322151</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1553,6 +1593,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129322456</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1665,6 +1710,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129322464</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1777,6 +1827,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129322521</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1889,6 +1944,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129322559</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2001,6 +2061,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129322600</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2108,6 +2173,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129322622</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2215,6 +2285,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129322635</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2322,6 +2397,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129322990</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2429,6 +2509,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129323037</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2536,6 +2621,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129323053</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2643,6 +2733,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129323106</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2750,6 +2845,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129323560</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2857,6 +2957,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129323568</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2964,6 +3069,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129323585</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3071,6 +3181,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129323677</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3188,6 +3303,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129321922</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3305,6 +3425,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129322534</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3417,6 +3542,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129322346</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3529,6 +3659,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129322929</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3655,6 +3790,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129321663</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3781,6 +3921,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129321689</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3907,6 +4052,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129321796</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4033,6 +4183,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129321871</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4140,6 +4295,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129321919</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4252,6 +4412,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129321974</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4378,6 +4543,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129323344</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4504,6 +4674,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129323359</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4611,6 +4786,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129323531</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4718,6 +4898,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129323543</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4825,8 +5010,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129323598</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>